--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44939</v>
+        <v>46050</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45147</v>
+        <v>44959</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45553</v>
+        <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44959</v>
+        <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46050</v>
+        <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45478</v>
+        <v>46234</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46190</v>
+        <v>44939</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44796</v>
+        <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44957</v>
+        <v>45553</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46234</v>
+        <v>44796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46234</v>
+        <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46050</v>
+        <v>44959</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44959</v>
+        <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46190</v>
+        <v>44796</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46234</v>
+        <v>45553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46234</v>
+        <v>46050</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44939</v>
+        <v>46190</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1562,14 +1562,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44957</v>
+        <v>45478</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45553</v>
+        <v>44957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45478</v>
+        <v>46234</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>44959</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44939</v>
+        <v>46050</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44796</v>
+        <v>44939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45553</v>
+        <v>44957</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46050</v>
+        <v>46190</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46190</v>
+        <v>45553</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1562,14 +1562,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45478</v>
+        <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44957</v>
+        <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46234</v>
+        <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44959</v>
+        <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46050</v>
+        <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45147</v>
+        <v>45553</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44939</v>
+        <v>44959</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44957</v>
+        <v>45478</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>46190</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45553</v>
+        <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46234</v>
+        <v>46050</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45478</v>
+        <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44939</v>
+        <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45147</v>
+        <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45553</v>
+        <v>46050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44959</v>
+        <v>44957</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45478</v>
+        <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46190</v>
+        <v>45553</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.6</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1491,7 +1491,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1562,14 +1562,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46234</v>
+        <v>45478</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46050</v>
+        <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44957</v>
+        <v>44959</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44957</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45553</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45478</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>44959</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45147</v>
+        <v>44959</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44939</v>
+        <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46050</v>
+        <v>46190</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44957</v>
+        <v>46050</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46190</v>
+        <v>44939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45553</v>
+        <v>44957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44796</v>
+        <v>45553</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1562,14 +1562,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45478</v>
+        <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46234</v>
+        <v>44796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44959</v>
+        <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44959</v>
+        <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46190</v>
+        <v>45478</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46050</v>
+        <v>45553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44939</v>
+        <v>46050</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44957</v>
+        <v>44796</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45553</v>
+        <v>44959</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46234</v>
+        <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44796</v>
+        <v>46190</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45478</v>
+        <v>46234</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44939</v>
+        <v>44959</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45478</v>
+        <v>46050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45553</v>
+        <v>44939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46050</v>
+        <v>44957</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44796</v>
+        <v>46190</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44959</v>
+        <v>45553</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44957</v>
+        <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46190</v>
+        <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46234</v>
+        <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44959</v>
+        <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44939</v>
+        <v>45553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44957</v>
+        <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46190</v>
+        <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45553</v>
+        <v>44959</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46234</v>
+        <v>44796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45478</v>
+        <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>45553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44959</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>44796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>45553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44959</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>44796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44939</v>
+        <v>44959</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45147</v>
+        <v>46050</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46050</v>
+        <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45553</v>
+        <v>44939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46190</v>
+        <v>44957</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45478</v>
+        <v>46190</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44959</v>
+        <v>45553</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46234</v>
+        <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44957</v>
+        <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44959</v>
+        <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46050</v>
+        <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45147</v>
+        <v>46050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44939</v>
+        <v>45553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44957</v>
+        <v>44959</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46190</v>
+        <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45553</v>
+        <v>46190</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
         <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1647,7 +1647,7 @@
         <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45478</v>
+        <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44939</v>
+        <v>44796</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45147</v>
+        <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46050</v>
+        <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45553</v>
+        <v>44957</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44959</v>
+        <v>45478</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45478</v>
+        <v>45553</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46190</v>
+        <v>44959</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44796</v>
+        <v>46050</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44957</v>
+        <v>46234</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44796</v>
+        <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44939</v>
+        <v>46050</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44957</v>
+        <v>45553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45478</v>
+        <v>44959</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45553</v>
+        <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44959</v>
+        <v>46190</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46050</v>
+        <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46190</v>
+        <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46234</v>
+        <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44939</v>
+        <v>46050</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46050</v>
+        <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45147</v>
+        <v>44959</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45553</v>
+        <v>44939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44959</v>
+        <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45478</v>
+        <v>44957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46190</v>
+        <v>46234</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46234</v>
+        <v>45553</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46234</v>
+        <v>44796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44957</v>
+        <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46050</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44959</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>44957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>46234</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>45553</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>44796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46050</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44959</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>44957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>46234</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>45553</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>44796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46050</v>
+        <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44959</v>
+        <v>46050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44939</v>
+        <v>45553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46190</v>
+        <v>44959</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44957</v>
+        <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46234</v>
+        <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45553</v>
+        <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45478</v>
+        <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44939</v>
+        <v>46050</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45147</v>
+        <v>44959</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46050</v>
+        <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45553</v>
+        <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>6.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44959</v>
+        <v>44939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45478</v>
+        <v>46234</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46190</v>
+        <v>46234</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44796</v>
+        <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46234</v>
+        <v>45553</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46234</v>
+        <v>44796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44957</v>
+        <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46050</v>
+        <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44959</v>
+        <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45147</v>
+        <v>45478</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46190</v>
+        <v>44959</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44939</v>
+        <v>45553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46234</v>
+        <v>44796</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46234</v>
+        <v>46050</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1562,14 +1562,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44957</v>
+        <v>46190</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45553</v>
+        <v>44957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45478</v>
+        <v>46234</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44939</v>
+        <v>44959</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45478</v>
+        <v>46050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44959</v>
+        <v>44939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45553</v>
+        <v>44957</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44796</v>
+        <v>45553</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46050</v>
+        <v>46190</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1562,14 +1562,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46190</v>
+        <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44957</v>
+        <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46234</v>
+        <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44959</v>
+        <v>44957</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45147</v>
+        <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46050</v>
+        <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44939</v>
+        <v>45478</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44957</v>
+        <v>45553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45553</v>
+        <v>44959</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46190</v>
+        <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44796</v>
+        <v>46050</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45478</v>
+        <v>46234</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>44957</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>45478</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>44959</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46050</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46190</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46234</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>44957</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>45478</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>44959</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46050</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46190</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46234</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44957</v>
+        <v>44796</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44939</v>
+        <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45147</v>
+        <v>45478</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45478</v>
+        <v>46234</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45553</v>
+        <v>46234</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44959</v>
+        <v>46050</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44796</v>
+        <v>44959</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46050</v>
+        <v>45147</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46190</v>
+        <v>44939</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46234</v>
+        <v>44957</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46234</v>
+        <v>45553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44796</v>
+        <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46190</v>
+        <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45478</v>
+        <v>44959</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46234</v>
+        <v>46050</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46234</v>
+        <v>45553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46050</v>
+        <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44959</v>
+        <v>46190</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45147</v>
+        <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44939</v>
+        <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44957</v>
+        <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45553</v>
+        <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44939</v>
+        <v>44959</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44959</v>
+        <v>46050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46050</v>
+        <v>44939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45553</v>
+        <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>6.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45478</v>
+        <v>44957</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46190</v>
+        <v>46234</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46234</v>
+        <v>45553</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46234</v>
+        <v>44796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44957</v>
+        <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44959</v>
+        <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45147</v>
+        <v>44959</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46050</v>
+        <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44939</v>
+        <v>45478</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46190</v>
+        <v>45553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.6</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44957</v>
+        <v>44796</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
         <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45553</v>
+        <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44796</v>
+        <v>44957</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45478</v>
+        <v>46050</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44939</v>
+        <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44959</v>
+        <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45147</v>
+        <v>46050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45478</v>
+        <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45553</v>
+        <v>44957</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44796</v>
+        <v>45553</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46190</v>
+        <v>46234</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
         <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46234</v>
+        <v>44796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1718,14 +1718,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44957</v>
+        <v>45478</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46050</v>
+        <v>44959</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>44957</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45553</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>46234</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>44796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45478</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>44959</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>44957</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>45553</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>46234</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>44796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45478</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>44959</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45147</v>
+        <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44939</v>
+        <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46050</v>
+        <v>45553</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46190</v>
+        <v>45478</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44957</v>
+        <v>46050</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45553</v>
+        <v>46190</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46234</v>
+        <v>44796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
         <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1718,14 +1718,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45478</v>
+        <v>44957</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1803,7 +1803,7 @@
         <v>44959</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44939</v>
+        <v>46050</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45553</v>
+        <v>44959</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45478</v>
+        <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46050</v>
+        <v>44939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46190</v>
+        <v>46234</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.6</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46234</v>
+        <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46234</v>
+        <v>45553</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44957</v>
+        <v>44796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44959</v>
+        <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46050</v>
+        <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44959</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46190</v>
+        <v>45553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.6</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44939</v>
+        <v>46050</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46234</v>
+        <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44957</v>
+        <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45553</v>
+        <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45478</v>
+        <v>44957</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44939</v>
+        <v>44957</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45147</v>
+        <v>44959</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44959</v>
+        <v>45553</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45553</v>
+        <v>44796</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46050</v>
+        <v>45478</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45478</v>
+        <v>46050</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1491,7 +1491,7 @@
         <v>46190</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46234</v>
+        <v>45147</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44957</v>
+        <v>44939</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44957</v>
+        <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44959</v>
+        <v>44957</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45553</v>
+        <v>46234</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45478</v>
+        <v>46050</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46050</v>
+        <v>44939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46190</v>
+        <v>44959</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46234</v>
+        <v>45147</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46234</v>
+        <v>45553</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1718,14 +1718,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45147</v>
+        <v>45478</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44939</v>
+        <v>44796</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>44957</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46234</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>46234</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>46050</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>44939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44959</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45147</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>45553</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45478</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>44796</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>44957</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>46234</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>46234</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>46050</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>44939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44959</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45147</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>45553</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45478</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>44796</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46190</v>
+        <v>44796</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44957</v>
+        <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46234</v>
+        <v>46050</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46050</v>
+        <v>44959</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44939</v>
+        <v>45147</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44959</v>
+        <v>46234</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45147</v>
+        <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45553</v>
+        <v>44939</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1718,14 +1718,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45478</v>
+        <v>44957</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44796</v>
+        <v>45553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE18"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44796</v>
+        <v>45553</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45478</v>
+        <v>44957</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46190</v>
+        <v>44939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46050</v>
+        <v>45147</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44959</v>
+        <v>45478</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45147</v>
+        <v>46050</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1491,7 +1491,7 @@
         <v>46234</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1569,7 +1569,7 @@
         <v>46234</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44939</v>
+        <v>44796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44957</v>
+        <v>44959</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45553</v>
+        <v>46190</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>6.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr"/>
     </row>
-    <row r="18">
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>S 2080-2026</t>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2016,6 +2016,84 @@
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S 2586-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VAXHOLM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45553</v>
+        <v>44939</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>44957</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44939</v>
+        <v>44959</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45147</v>
+        <v>45553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45478</v>
+        <v>44796</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>46050</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 32204-2026</t>
+          <t>A 28612-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 32127-2026</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1562,14 +1562,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46234</v>
+        <v>45478</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 32127-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44796</v>
+        <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 32204-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44959</v>
+        <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28612-2026</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46190</v>
+        <v>45147</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>46296</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>

--- a/Översikt VAXHOLM.xlsx
+++ b/Översikt VAXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45372</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>46234</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44524</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2229-2023</t>
+          <t>A 6004-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44939</v>
+        <v>46050</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5528-2023</t>
+          <t>A 5968-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44957</v>
+        <v>44959</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 5968-2023</t>
+          <t>A 35838-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44959</v>
+        <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 39876-2024</t>
+          <t>A 2229-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1250,14 +1250,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45553</v>
+        <v>44939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34926-2022</t>
+          <t>A 5528-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44796</v>
+        <v>44957</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 6004-2026</t>
+          <t>A 39876-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46050</v>
+        <v>45553</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1491,7 +1491,7 @@
         <v>46190</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28815-2024</t>
+          <t>A 34926-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1562,14 +1562,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45478</v>
+        <v>44796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46234</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 35838-2023</t>
+          <t>A 28815-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45147</v>
+        <v>45478</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46231</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>46296</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
